--- a/data/trans_orig/P19C07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37148</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>63419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>663466</t>
+          <t>661683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679039</t>
+          <t>678117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>914206</t>
+          <t>914684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>936447</t>
+          <t>935956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1582335</t>
+          <t>1584905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1611176</t>
+          <t>1610908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70025</t>
+          <t>68792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41464</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70252</t>
+          <t>71534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88907</t>
+          <t>89375</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131059</t>
+          <t>131544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1244423</t>
+          <t>1245656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1273945</t>
+          <t>1273947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1302943</t>
+          <t>1301661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1331731</t>
+          <t>1331142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2556584</t>
+          <t>2556099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2598736</t>
+          <t>2598268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>429074</t>
+          <t>428090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>443370</t>
+          <t>443365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392705</t>
+          <t>392441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404860</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>825942</t>
+          <t>826440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>844924</t>
+          <t>845313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66285</t>
+          <t>66970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103953</t>
+          <t>104631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>77052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117081</t>
+          <t>115636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156069</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208510</t>
+          <t>205090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2350789</t>
+          <t>2350111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2388457</t>
+          <t>2387772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2623856</t>
+          <t>2625301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2663410</t>
+          <t>2663885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4987169</t>
+          <t>4990589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5039610</t>
+          <t>5041611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23717</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>49369</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>755139</t>
+          <t>755226</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>771001</t>
+          <t>771550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1094719</t>
+          <t>1094980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1114356</t>
+          <t>1114488</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1859665</t>
+          <t>1858046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1883698</t>
+          <t>1882922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49329</t>
+          <t>47973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81710</t>
+          <t>82918</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57788</t>
+          <t>57067</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91865</t>
+          <t>91799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114077</t>
+          <t>115384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164521</t>
+          <t>161481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1606568</t>
+          <t>1605360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1638949</t>
+          <t>1640305</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1498413</t>
+          <t>1498479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1532490</t>
+          <t>1533211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3114034</t>
+          <t>3117074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3164478</t>
+          <t>3163171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29877</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10493</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>28371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52727</t>
+          <t>52537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412257</t>
+          <t>411671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430435</t>
+          <t>430522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>393960</t>
+          <t>395352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>413230</t>
+          <t>412735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813130</t>
+          <t>813320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>838561</t>
+          <t>837786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>79247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117505</t>
+          <t>120723</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91399</t>
+          <t>92021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137226</t>
+          <t>134279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180044</t>
+          <t>183924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241733</t>
+          <t>242637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2792081</t>
+          <t>2788863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2831446</t>
+          <t>2830339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3005017</t>
+          <t>3007964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3050844</t>
+          <t>3050222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5810095</t>
+          <t>5809191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5871784</t>
+          <t>5867904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>27721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443534</t>
+          <t>444530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454642</t>
+          <t>454673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>611129</t>
+          <t>611153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>628538</t>
+          <t>628837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1061542</t>
+          <t>1060413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1081430</t>
+          <t>1081538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>47405</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78930</t>
+          <t>79138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53712</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85018</t>
+          <t>84890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>108326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155465</t>
+          <t>153151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1617675</t>
+          <t>1617467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1648605</t>
+          <t>1649200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1623701</t>
+          <t>1623829</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1655007</t>
+          <t>1654445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3249859</t>
+          <t>3252173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3294245</t>
+          <t>3296998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>25857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483072</t>
+          <t>483948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495180</t>
+          <t>495304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>482290</t>
+          <t>482463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>499937</t>
+          <t>499692</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971135</t>
+          <t>971637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>992146</t>
+          <t>992288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59504</t>
+          <t>59808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94486</t>
+          <t>93306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82182</t>
+          <t>82959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122565</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150190</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203983</t>
+          <t>206240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2558783</t>
+          <t>2559963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2593765</t>
+          <t>2593461</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2733348</t>
+          <t>2733034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2773731</t>
+          <t>2772954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5305199</t>
+          <t>5302942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5358992</t>
+          <t>5355129</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27694</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43339</t>
+          <t>42147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>463690</t>
+          <t>464725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>478108</t>
+          <t>478125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>693922</t>
+          <t>693489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>706993</t>
+          <t>706770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1162718</t>
+          <t>1163910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1182076</t>
+          <t>1182049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107851</t>
+          <t>104902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,49 +5900,49 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>83267</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>58819</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>106270</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>4,84%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83267</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>57429</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>106643</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>160</t>
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122417</t>
+          <t>123720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195494</t>
+          <t>196530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2122686</t>
+          <t>2125635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2180162</t>
+          <t>2182592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,47 +6013,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2749</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2114639</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2091636</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2139087</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>95,16%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2749</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2114639</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2091263</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2140477</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4232948</t>
+          <t>4231912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4306025</t>
+          <t>4304722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>31331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24617</t>
+          <t>24746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72367</t>
+          <t>69935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601117</t>
+          <t>599985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618400</t>
+          <t>618795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>603059</t>
+          <t>604798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626994</t>
+          <t>626865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1210560</t>
+          <t>1212992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1240043</t>
+          <t>1240622</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78659</t>
+          <t>78577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138339</t>
+          <t>139222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110380</t>
+          <t>111424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164804</t>
+          <t>165652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204202</t>
+          <t>206582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>285533</t>
+          <t>286812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3207954</t>
+          <t>3207071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3267634</t>
+          <t>3267716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3406329</t>
+          <t>3405481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3460753</t>
+          <t>3459709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6672803</t>
+          <t>6672804</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6631893</t>
+          <t>6630615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6713224</t>
+          <t>6710845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P19C07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>26660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>44570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63419</t>
+          <t>64723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661683</t>
+          <t>662705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>678117</t>
+          <t>679199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>914684</t>
+          <t>914389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>935956</t>
+          <t>934909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1584905</t>
+          <t>1583601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1610908</t>
+          <t>1610276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40501</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68792</t>
+          <t>67894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>41713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71534</t>
+          <t>72199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89375</t>
+          <t>89482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131544</t>
+          <t>128912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1245656</t>
+          <t>1246554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1273947</t>
+          <t>1275803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1301661</t>
+          <t>1300996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1331142</t>
+          <t>1331482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2556099</t>
+          <t>2558731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2598268</t>
+          <t>2598161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>22210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>428090</t>
+          <t>428719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>443365</t>
+          <t>443126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392441</t>
+          <t>393128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404853</t>
+          <t>405206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>826440</t>
+          <t>827523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>845313</t>
+          <t>845015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66970</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104631</t>
+          <t>103332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115636</t>
+          <t>115038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154068</t>
+          <t>152983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205090</t>
+          <t>207455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2350111</t>
+          <t>2351410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2387772</t>
+          <t>2387395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2625301</t>
+          <t>2625899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2663885</t>
+          <t>2662803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4990589</t>
+          <t>4988224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5041611</t>
+          <t>5042696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>23739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>755226</t>
+          <t>755435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>771550</t>
+          <t>771961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1094980</t>
+          <t>1095370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1114488</t>
+          <t>1114324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1858046</t>
+          <t>1857906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1882922</t>
+          <t>1883156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47973</t>
+          <t>49945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82918</t>
+          <t>84469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57067</t>
+          <t>57112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91799</t>
+          <t>92549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115384</t>
+          <t>115825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161481</t>
+          <t>163243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1605360</t>
+          <t>1603809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1640305</t>
+          <t>1638333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1498479</t>
+          <t>1497729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1533211</t>
+          <t>1533166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3117074</t>
+          <t>3115312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3163171</t>
+          <t>3162730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30463</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28371</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52537</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>411671</t>
+          <t>411390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430522</t>
+          <t>430128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>395352</t>
+          <t>393754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>412735</t>
+          <t>412337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813320</t>
+          <t>812747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>837786</t>
+          <t>838959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79247</t>
+          <t>79459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120723</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92021</t>
+          <t>94386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134279</t>
+          <t>135399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183924</t>
+          <t>181566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242637</t>
+          <t>241068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2788863</t>
+          <t>2791517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2830339</t>
+          <t>2830127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3007964</t>
+          <t>3006844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3050222</t>
+          <t>3047857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5809191</t>
+          <t>5810760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5867904</t>
+          <t>5870262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27721</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444530</t>
+          <t>445475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454673</t>
+          <t>455392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>611153</t>
+          <t>610688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>628837</t>
+          <t>628545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1060413</t>
+          <t>1061119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1081538</t>
+          <t>1080838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47405</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79138</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84890</t>
+          <t>83559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>107245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153151</t>
+          <t>151363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1617467</t>
+          <t>1617900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1649200</t>
+          <t>1649023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1623829</t>
+          <t>1625160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1654445</t>
+          <t>1656673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3252173</t>
+          <t>3253961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3296998</t>
+          <t>3298079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483948</t>
+          <t>482893</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495304</t>
+          <t>495182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>482463</t>
+          <t>482585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>499301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971637</t>
+          <t>971529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>992288</t>
+          <t>992142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59808</t>
+          <t>60165</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93306</t>
+          <t>94608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82959</t>
+          <t>81826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122879</t>
+          <t>122652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154053</t>
+          <t>149440</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206240</t>
+          <t>203272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2559963</t>
+          <t>2558661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2593461</t>
+          <t>2593104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2733034</t>
+          <t>2733261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2772954</t>
+          <t>2774087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5302942</t>
+          <t>5305910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5355129</t>
+          <t>5359742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31966</t>
+          <t>36110</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42147</t>
+          <t>46848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>472917</t>
+          <t>525217</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464725</t>
+          <t>516675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>478125</t>
+          <t>531234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>701174</t>
+          <t>760545</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>693489</t>
+          <t>752200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>706770</t>
+          <t>767348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1174091</t>
+          <t>1285761</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1163910</t>
+          <t>1275023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1182049</t>
+          <t>1294960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>82799</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104902</t>
+          <t>108749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,67 +5915,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83267</t>
+          <t>91684</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106270</t>
+          <t>114426</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>174483</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>147116</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>206233</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>4,84%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>157932</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>123720</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>196530</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2155872</t>
+          <t>2063679</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2125635</t>
+          <t>2037729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2182592</t>
+          <t>2084275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,67 +6028,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2114639</t>
+          <t>2018908</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2091636</t>
+          <t>1996166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2139087</t>
+          <t>2036128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4082587</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4050837</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4109954</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>95,16%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4612</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4270510</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4231912</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4304722</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>32542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46813</t>
+          <t>48609</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54725</t>
+          <t>58075</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69935</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>611241</t>
+          <t>680146</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>599985</t>
+          <t>669299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618795</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>616961</t>
+          <t>688033</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>604798</t>
+          <t>675804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626865</t>
+          <t>698088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1228202</t>
+          <t>1368179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1212992</t>
+          <t>1352712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1240622</t>
+          <t>1382150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>106265</t>
+          <t>116556</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78577</t>
+          <t>95002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139222</t>
+          <t>145880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111424</t>
+          <t>129896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165652</t>
+          <t>179535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>244623</t>
+          <t>268667</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206582</t>
+          <t>237082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286812</t>
+          <t>309020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3240028</t>
+          <t>3269042</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3207071</t>
+          <t>3239718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3267716</t>
+          <t>3290596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3432775</t>
+          <t>3467486</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3405481</t>
+          <t>3440062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3459709</t>
+          <t>3489701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6672804</t>
+          <t>6736528</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6630615</t>
+          <t>6696175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6710845</t>
+          <t>6768113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
